--- a/scripts/Bulk_Upload_Template.xlsx
+++ b/scripts/Bulk_Upload_Template.xlsx
@@ -397,7 +397,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:M7"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,9 +431,27 @@
         <v>Price</v>
       </c>
       <c r="F1" t="str">
+        <v>Color</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Material</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Shape</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Finish</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Dimensions</v>
+      </c>
+      <c r="K1" t="str">
         <v>Sizes and Stock</v>
       </c>
-      <c r="G1" t="str">
+      <c r="L1" t="str">
+        <v>Stock</v>
+      </c>
+      <c r="M1" t="str">
         <v>Image Filenames</v>
       </c>
     </row>
@@ -439,21 +472,39 @@
         <v>1499</v>
       </c>
       <c r="F2" t="str">
+        <v>Red</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Velvet</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
         <v>S:10, M:20, L:15, XL:5</v>
       </c>
-      <c r="G2" t="str">
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>red-dress-1.jpg, red-dress-2.png</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Blue Denim Jacket</v>
+        <v>High Rise Mom Jeans</v>
       </c>
       <c r="B3" t="str">
-        <v>Classic oversized blue denim jacket.</v>
+        <v>Relaxed high rise jeans.</v>
       </c>
       <c r="C3" t="str">
-        <v>jackets</v>
+        <v>bottoms-jeans</v>
       </c>
       <c r="D3">
         <v>2999</v>
@@ -462,15 +513,197 @@
         <v>2499</v>
       </c>
       <c r="F3" t="str">
-        <v>M:10, L:10</v>
+        <v>Blue</v>
       </c>
       <c r="G3" t="str">
-        <v>denim-front.jpg</v>
+        <v>Denim</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>28:5, 30:10, 32:10</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v>jeans-front.jpg</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Tan Leather Tote</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Roomy everyday tote.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>totes</v>
+      </c>
+      <c r="D4">
+        <v>3999</v>
+      </c>
+      <c r="E4">
+        <v>3499</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Tan</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Vegan Leather</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>30 x 12 x 25 cm</v>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>25</v>
+      </c>
+      <c r="M4" t="str">
+        <v>tote-1.jpg</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Pearl Drop Earrings</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Lightweight pearl drops.</v>
+      </c>
+      <c r="C5" t="str">
+        <v>earrings</v>
+      </c>
+      <c r="D5">
+        <v>799</v>
+      </c>
+      <c r="E5">
+        <v>599</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Gold</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Brass</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>40</v>
+      </c>
+      <c r="M5" t="str">
+        <v>earrings-1.jpg</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Adjustable Stone Ring</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Adjustable ring with a stone.</v>
+      </c>
+      <c r="C6" t="str">
+        <v>rings</v>
+      </c>
+      <c r="D6">
+        <v>699</v>
+      </c>
+      <c r="E6">
+        <v>499</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Silver</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Sterling Silver</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>6:5, 7:5, 8:5</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>ring-1.jpg</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Glossy Almond Press-on Set</v>
+      </c>
+      <c r="B7" t="str">
+        <v>24 piece press-on set.</v>
+      </c>
+      <c r="C7" t="str">
+        <v>press-on-sets</v>
+      </c>
+      <c r="D7">
+        <v>999</v>
+      </c>
+      <c r="E7">
+        <v>799</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>Almond</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Glossy</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>XS:10, S:10, M:10, L:10</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>nails-1.jpg</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
   </ignoredErrors>
 </worksheet>
 </file>